--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard.guevara\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793A058F-1EC0-4346-9160-40AD7F37F74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04394AEC-A8C3-4390-9E75-E4CC897EFA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
+    <workbookView xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{3BC2DC06-783A-43D0-92A7-AD72905E1BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="90">
   <si>
     <t>Cargo</t>
   </si>
@@ -283,6 +283,27 @@
   </si>
   <si>
     <t>Tecnico B</t>
+  </si>
+  <si>
+    <t>AA26</t>
+  </si>
+  <si>
+    <t>AA27</t>
+  </si>
+  <si>
+    <t>Supervisor 1</t>
+  </si>
+  <si>
+    <t>Supervisor 2</t>
+  </si>
+  <si>
+    <t>Supervisor 3</t>
+  </si>
+  <si>
+    <t>Supervisor 4</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
   </si>
 </sst>
 </file>
@@ -668,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3A4F7D-E435-4C0F-BEEB-5D04FE807857}">
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.81640625" style="1" customWidth="1"/>
@@ -697,16 +718,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="B2" s="1">
-        <v>11204332</v>
+        <v>1111111</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D2" s="1">
+        <v>5000000</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -714,16 +735,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1">
-        <v>33819510</v>
+        <v>2222222</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D3" s="1">
+        <v>5000000</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -731,16 +752,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1">
-        <v>35379078</v>
+        <v>3333333</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5000000</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -748,16 +769,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1">
-        <v>39724105</v>
+        <v>444444</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="2">
-        <v>4028000</v>
+        <v>89</v>
+      </c>
+      <c r="D5" s="1">
+        <v>5000000</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -765,10 +786,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1">
-        <v>79822166</v>
+        <v>11204332</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>80</v>
@@ -782,10 +803,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B7" s="1">
-        <v>80208472</v>
+        <v>33819510</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>80</v>
@@ -799,10 +820,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1">
-        <v>80213057</v>
+        <v>35379078</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>80</v>
@@ -816,10 +837,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1">
-        <v>80251217</v>
+        <v>39724105</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>80</v>
@@ -833,16 +854,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" s="1">
-        <v>80830605</v>
+        <v>79822166</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4028000</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -850,16 +871,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1">
-        <v>80912134</v>
+        <v>80208472</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4028000</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>3</v>
@@ -867,16 +888,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>93138251</v>
+        <v>80213057</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4028000</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>3</v>
@@ -884,16 +905,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1">
-        <v>93298014</v>
+        <v>80251217</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="3">
-        <v>2968000</v>
+        <v>80</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4028000</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>3</v>
@@ -901,10 +922,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B14" s="1">
-        <v>94446125</v>
+        <v>80830605</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>81</v>
@@ -918,10 +939,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B15" s="1">
-        <v>1000272392</v>
+        <v>80912134</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>81</v>
@@ -935,10 +956,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B16" s="1">
-        <v>1010044018</v>
+        <v>93138251</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>81</v>
@@ -952,10 +973,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1">
-        <v>1012406573</v>
+        <v>93298014</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>81</v>
@@ -969,10 +990,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1">
-        <v>1012466465</v>
+        <v>94446125</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>81</v>
@@ -986,10 +1007,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B19" s="1">
-        <v>1013614915</v>
+        <v>1000272392</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>81</v>
@@ -1003,10 +1024,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="1">
-        <v>1013630135</v>
+        <v>1010044018</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>81</v>
@@ -1020,10 +1041,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1">
-        <v>1014192228</v>
+        <v>1012406573</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>81</v>
@@ -1037,10 +1058,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1">
-        <v>1014232367</v>
+        <v>1012466465</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>81</v>
@@ -1054,10 +1075,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1">
-        <v>1014238905</v>
+        <v>1013614915</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>81</v>
@@ -1071,10 +1092,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1">
-        <v>1014248976</v>
+        <v>1013630135</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>81</v>
@@ -1088,10 +1109,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1">
-        <v>1016039845</v>
+        <v>1014192228</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>81</v>
@@ -1105,10 +1126,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1">
-        <v>1016066574</v>
+        <v>1014232367</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>81</v>
@@ -1122,10 +1143,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B27" s="1">
-        <v>1018432981</v>
+        <v>1014238905</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>81</v>
@@ -1139,10 +1160,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1">
-        <v>1018434197</v>
+        <v>1014248976</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>81</v>
@@ -1156,10 +1177,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1">
-        <v>1019131043</v>
+        <v>1016039845</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>81</v>
@@ -1173,10 +1194,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1">
-        <v>1020792634</v>
+        <v>1016066574</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>81</v>
@@ -1190,10 +1211,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B31" s="1">
-        <v>1022370155</v>
+        <v>1018432981</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>81</v>
@@ -1207,10 +1228,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="1">
-        <v>1022971025</v>
+        <v>1018434197</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>81</v>
@@ -1224,10 +1245,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="1">
-        <v>1024512643</v>
+        <v>1019131043</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>81</v>
@@ -1241,10 +1262,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B34" s="1">
-        <v>1024534468</v>
+        <v>1020792634</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>81</v>
@@ -1258,10 +1279,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35" s="1">
-        <v>1024593756</v>
+        <v>1022370155</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>81</v>
@@ -1275,10 +1296,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B36" s="1">
-        <v>1030578335</v>
+        <v>1022971025</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>81</v>
@@ -1292,10 +1313,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B37" s="1">
-        <v>1030592271</v>
+        <v>1024512643</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>81</v>
@@ -1309,16 +1330,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="B38" s="1">
-        <v>1030635367</v>
+        <v>1024534468</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D38" s="3">
+        <v>2968000</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>3</v>
@@ -1326,16 +1347,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="B39" s="1">
-        <v>1031142560</v>
+        <v>1024593756</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2968000</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>3</v>
@@ -1343,16 +1364,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1">
-        <v>1032416590</v>
+        <v>1030578335</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2968000</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>3</v>
@@ -1360,16 +1381,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B41" s="1">
-        <v>1054681147</v>
+        <v>1030592271</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" s="2">
-        <v>2544000</v>
+        <v>81</v>
+      </c>
+      <c r="D41" s="3">
+        <v>2968000</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>3</v>
@@ -1377,10 +1398,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1">
-        <v>1072719991</v>
+        <v>1030635367</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>82</v>
@@ -1394,10 +1415,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1">
-        <v>1073234269</v>
+        <v>1031142560</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>82</v>
@@ -1411,10 +1432,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1">
-        <v>1073687003</v>
+        <v>1032416590</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>82</v>
@@ -1428,10 +1449,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B45" s="1">
-        <v>1073721158</v>
+        <v>1054681147</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>82</v>
@@ -1445,10 +1466,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B46" s="1">
-        <v>1078180826</v>
+        <v>1072719991</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>82</v>
@@ -1462,10 +1483,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1">
-        <v>1097332216</v>
+        <v>1073234269</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>82</v>
@@ -1479,10 +1500,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="B48" s="1">
-        <v>1127621316</v>
+        <v>1073687003</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>82</v>
@@ -1496,10 +1517,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="B49" s="1">
-        <v>1129568417</v>
+        <v>1073721158</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>82</v>
@@ -1513,13 +1534,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1078180826</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D50" s="2">
+        <v>2544000</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>3</v>
@@ -1527,13 +1551,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
-        <v>7</v>
+        <v>55</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1097332216</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2544000</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>3</v>
@@ -1541,13 +1568,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="B52" s="1">
+        <v>1127621316</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D52" s="2">
+        <v>2544000</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>3</v>
@@ -1555,13 +1585,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1129568417</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="3">
-        <v>1751000</v>
+        <v>82</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2544000</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>3</v>
@@ -1569,7 +1602,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
@@ -1583,7 +1616,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>5</v>
@@ -1597,7 +1630,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>5</v>
@@ -1611,7 +1644,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>5</v>
@@ -1625,7 +1658,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>5</v>
@@ -1639,7 +1672,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>5</v>
@@ -1653,7 +1686,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>5</v>
@@ -1667,7 +1700,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>5</v>
@@ -1681,7 +1714,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>5</v>
@@ -1695,7 +1728,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -1709,7 +1742,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>5</v>
@@ -1723,7 +1756,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>5</v>
@@ -1737,7 +1770,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>5</v>
@@ -1751,7 +1784,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>5</v>
@@ -1765,7 +1798,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>5</v>
@@ -1779,7 +1812,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
@@ -1793,7 +1826,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>5</v>
@@ -1807,7 +1840,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>5</v>
@@ -1821,7 +1854,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>5</v>
@@ -1835,7 +1868,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>5</v>
@@ -1849,15 +1882,99 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="3">
-        <v>1751000</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="C78" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1751000</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>3</v>
       </c>
     </row>
